--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6141087</v>
+        <v>82402749</v>
       </c>
       <c r="B4" t="n">
-        <v>104404</v>
+        <v>57576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,42 +931,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>100117</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lindreservatets NR, Öl</t>
+          <t>2, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622267.9069621958</v>
+        <v>622726.9035858739</v>
       </c>
       <c r="R4" t="n">
-        <v>6354807.634726372</v>
+        <v>6354755.979695073</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +1004,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-07-14</t>
+          <t>2014-04-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1000,7 +1014,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-07-14</t>
+          <t>2014-04-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1008,6 +1022,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4 st sammanhängande kärr, stora delar kan torka ut. 100 % inventerad. Fin lokal. Bifynd av mindre vattensalamander</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,31 +1035,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>betesmark på sand, öppna markblottor</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pia Hertonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82402749</v>
+        <v>6141087</v>
       </c>
       <c r="B5" t="n">
-        <v>57576</v>
+        <v>104404</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,56 +1067,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100117</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2, Öl</t>
+          <t>Lindreservatets NR, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622726.9035858739</v>
+        <v>622267.9069621958</v>
       </c>
       <c r="R5" t="n">
-        <v>6354755.979695073</v>
+        <v>6354807.634726372</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
+          <t>2010-07-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-04-15</t>
+          <t>2010-07-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1144,11 +1144,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 st sammanhängande kärr, stora delar kan torka ut. 100 % inventerad. Fin lokal. Bifynd av mindre vattensalamander</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1157,16 +1152,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>betesmark på sand, öppna markblottor</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Pia Hertonsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Hertonsson, Marika Stenberg, Erik Fridolf, Per Nyström, Lars-Göran Pärlklint</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1817,6 +1817,118 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125688519</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindreservatet, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622315</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6354786</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -1822,12 +1822,7 @@
         <v>125688519</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -1822,7 +1822,7 @@
         <v>125688519</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14767-2020 artfynd.xlsx
+++ b/artfynd/A 14767-2020 artfynd.xlsx
@@ -1822,7 +1822,7 @@
         <v>125688519</v>
       </c>
       <c r="B11" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
